--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1455-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1455-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F387D00B-1C34-47FE-8C6D-A8D00523EBDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2F1ACAE-19EF-4DAE-A4F6-A0827E28DE86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{65208B54-EAAF-47CA-B2FD-F945A04453E1}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{CE59BC90-DC98-4600-9ADE-8760E5829BB1}"/>
   </bookViews>
   <sheets>
     <sheet name="1455-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1583,28 +1583,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B3997E0-DE92-4A1C-B634-6B3B5ADC92C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD68BA79-5DAF-415F-ABB3-E848741421C7}">
   <dimension ref="A1:X43"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="6" width="6" customWidth="1"/>
-    <col min="7" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1638,7 +1637,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1674,7 +1673,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1726,7 +1725,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1794,7 +1793,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1866,7 +1865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1938,7 +1937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -2010,7 +2009,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2082,7 +2081,7 @@
         <v>8.8800000000000008</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2154,7 +2153,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2226,7 +2225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2298,7 +2297,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2370,7 +2369,7 @@
         <v>4.57</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2442,7 +2441,7 @@
         <v>3.59</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2514,7 +2513,7 @@
         <v>2.67</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2586,7 +2585,7 @@
         <v>2.66</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2013</v>
       </c>
@@ -2658,7 +2657,7 @@
         <v>2.52</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2012</v>
       </c>
@@ -2730,7 +2729,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2011</v>
       </c>
@@ -2802,7 +2801,7 @@
         <v>2.54</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="41">
         <v>2010</v>
       </c>
@@ -2874,7 +2873,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="43"/>
       <c r="B20" s="44"/>
       <c r="C20" s="18" t="s">
@@ -2902,7 +2901,7 @@
       <c r="W20" s="50"/>
       <c r="X20" s="46"/>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="51">
         <v>2009</v>
       </c>
@@ -2974,7 +2973,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="53"/>
       <c r="B22" s="54"/>
       <c r="C22" s="20" t="s">
@@ -3002,7 +3001,7 @@
       <c r="W22" s="60"/>
       <c r="X22" s="56"/>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2008</v>
       </c>
@@ -3074,7 +3073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2007</v>
       </c>
@@ -3146,7 +3145,7 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2006</v>
       </c>
@@ -3218,7 +3217,7 @@
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2005</v>
       </c>
@@ -3290,7 +3289,7 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="41">
         <v>2004</v>
       </c>
@@ -3362,7 +3361,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="43"/>
       <c r="B28" s="44"/>
       <c r="C28" s="18" t="s">
@@ -3390,7 +3389,7 @@
       <c r="W28" s="50"/>
       <c r="X28" s="46"/>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="51">
         <v>2003</v>
       </c>
@@ -3462,7 +3461,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="53"/>
       <c r="B30" s="54"/>
       <c r="C30" s="20" t="s">
@@ -3490,7 +3489,7 @@
       <c r="W30" s="60"/>
       <c r="X30" s="56"/>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2002</v>
       </c>
@@ -3562,7 +3561,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="39">
         <v>2001</v>
       </c>
@@ -3634,7 +3633,7 @@
         <v>3.45</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2000</v>
       </c>
@@ -3706,7 +3705,7 @@
         <v>3.03</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="39">
         <v>1999</v>
       </c>
@@ -3778,7 +3777,7 @@
         <v>21.4</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>1998</v>
       </c>
@@ -3850,7 +3849,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="39">
         <v>1997</v>
       </c>
@@ -3922,7 +3921,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>1996</v>
       </c>
@@ -3994,7 +3993,7 @@
         <v>9.39</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="39">
         <v>1995</v>
       </c>
@@ -4066,7 +4065,7 @@
         <v>6.64</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>1994</v>
       </c>
@@ -4138,7 +4137,7 @@
         <v>8.85</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="39">
         <v>1993</v>
       </c>
@@ -4210,7 +4209,7 @@
         <v>7.41</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>1992</v>
       </c>
@@ -4282,7 +4281,7 @@
         <v>4.78</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="39">
         <v>1991</v>
       </c>
@@ -4354,7 +4353,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="37" t="s">
         <v>63</v>
       </c>
